--- a/app/src/main/assets/methodmesh/odk_templates/signals/example_odk_showcase_signal_morse_receive.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/signals/example_odk_showcase_signal_morse_receive.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R9a011a7cc6c74662"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R08c021190d004e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R8c4253dbe5ea4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R22b25f345a384bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R70d902dd2115443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rdc6d14a5951d4f91"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -358,7 +358,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="J3" s="8" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='signal.morse.receive',input_source=${morse_rx_source},input_dot_ms=${morse_rx_dot_ms},input_auto_timing=${morse_rx_auto_timing},input_optical_profile=${morse_rx_optical_profile},input_microphone_tone_hz=${morse_rx_tone_hz},input_microphone_tolerance_hz=${morse_rx_tolerance_hz},input_microphone_min_dbfs=${morse_rx_min_dbfs},input_element_gap_units=${morse_rx_element_gap},input_letter_gap_units=${morse_rx_letter_gap},input_word_gap_units=${morse_rx_word_gap},input_payload_mode='FULL',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='signal.morse.receive',input_source=${morse_rx_source},input_dot_ms=${morse_rx_dot_ms},input_auto_timing=${morse_rx_auto_timing},input_optical_profile=${morse_rx_optical_profile},input_colour_assist=${morse_rx_colour_assist},input_microphone_tone_hz=${morse_rx_tone_hz},input_microphone_tolerance_hz=${morse_rx_tolerance_hz},input_microphone_min_dbfs=${morse_rx_min_dbfs},input_element_gap_units=${morse_rx_element_gap},input_letter_gap_units=${morse_rx_letter_gap},input_word_gap_units=${morse_rx_word_gap},input_payload_mode='FULL',return_mode='flat')</x:v>
       </x:c>
       <x:c r="K3" s="8"/>
     </x:row>
@@ -391,10 +391,10 @@
         <x:v>morse_rx_dot_ms</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
-        <x:v>Expected speed</x:v>
+        <x:v>Expected / starting speed</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
-        <x:v>Choose the same nominal speed as TX.</x:v>
+        <x:v>For Manual this is only a weak starting prior; camera/audio can match the transmitter's nominal speed.</x:v>
       </x:c>
       <x:c r="E5" s="8" t="str">
         <x:v>yes</x:v>
@@ -454,22 +454,22 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
-        <x:v>select_one morse_tone</x:v>
+        <x:v>select_one colour_assist</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>morse_rx_tone_hz</x:v>
+        <x:v>morse_rx_colour_assist</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Microphone tone preset</x:v>
+        <x:v>Colour assist</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>Exactly the same A–D carrier catalogue as TX.</x:v>
+        <x:v>Auto calibrates white acquisition dots and red START; falls back to timing-only if colour is weak.</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
       <x:c r="F8" s="8" t="str">
-        <x:v>${morse_rx_source}='microphone'</x:v>
+        <x:v>${morse_rx_source}='camera' and ${morse_rx_optical_profile}='screen'</x:v>
       </x:c>
       <x:c r="G8" s="8"/>
       <x:c r="H8" s="8"/>
@@ -479,15 +479,17 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
-        <x:v>select_one tone_tol</x:v>
+        <x:v>select_one morse_tone</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>morse_rx_tolerance_hz</x:v>
+        <x:v>morse_rx_tone_hz</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Tone tolerance</x:v>
-      </x:c>
-      <x:c r="D9" s="8"/>
+        <x:v>Microphone tone preset</x:v>
+      </x:c>
+      <x:c r="D9" s="8" t="str">
+        <x:v>Exactly the same A–D carrier catalogue as TX.</x:v>
+      </x:c>
       <x:c r="E9" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -502,17 +504,15 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
-        <x:v>select_one dbfs</x:v>
+        <x:v>select_one tone_tol</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>morse_rx_min_dbfs</x:v>
+        <x:v>morse_rx_tolerance_hz</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Minimum microphone level</x:v>
-      </x:c>
-      <x:c r="D10" s="8" t="str">
-        <x:v>0 dBFS is full scale; more-negative thresholds detect quieter signals.</x:v>
-      </x:c>
+        <x:v>Tone tolerance</x:v>
+      </x:c>
+      <x:c r="D10" s="8"/>
       <x:c r="E10" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
@@ -527,19 +527,23 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
-        <x:v>select_one element_gap</x:v>
+        <x:v>select_one dbfs</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>morse_rx_element_gap</x:v>
+        <x:v>morse_rx_min_dbfs</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Element gap</x:v>
-      </x:c>
-      <x:c r="D11" s="8"/>
+        <x:v>Minimum microphone level</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="str">
+        <x:v>0 dBFS is full scale; more-negative thresholds detect quieter signals.</x:v>
+      </x:c>
       <x:c r="E11" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="F11" s="8"/>
+      <x:c r="F11" s="8" t="str">
+        <x:v>${morse_rx_source}='microphone'</x:v>
+      </x:c>
       <x:c r="G11" s="8"/>
       <x:c r="H11" s="8"/>
       <x:c r="I11" s="8"/>
@@ -548,13 +552,13 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
-        <x:v>select_one letter_gap</x:v>
+        <x:v>select_one element_gap</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>morse_rx_letter_gap</x:v>
+        <x:v>morse_rx_element_gap</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Letter gap</x:v>
+        <x:v>Element gap</x:v>
       </x:c>
       <x:c r="D12" s="8"/>
       <x:c r="E12" s="8" t="str">
@@ -569,13 +573,13 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
-        <x:v>select_one word_gap</x:v>
+        <x:v>select_one letter_gap</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>morse_rx_word_gap</x:v>
+        <x:v>morse_rx_letter_gap</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Word gap</x:v>
+        <x:v>Letter gap</x:v>
       </x:c>
       <x:c r="D13" s="8"/>
       <x:c r="E13" s="8" t="str">
@@ -590,38 +594,34 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>select_one word_gap</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>methodmesh_status</x:v>
+        <x:v>morse_rx_word_gap</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>MethodMesh status</x:v>
-      </x:c>
-      <x:c r="D14" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E14" s="8"/>
+        <x:v>Word gap</x:v>
+      </x:c>
+      <x:c r="D14" s="8"/>
+      <x:c r="E14" s="8" t="str">
+        <x:v>yes</x:v>
+      </x:c>
       <x:c r="F14" s="8"/>
       <x:c r="G14" s="8"/>
       <x:c r="H14" s="8"/>
-      <x:c r="I14" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
+      <x:c r="I14" s="8"/>
       <x:c r="J14" s="8"/>
-      <x:c r="K14" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
+      <x:c r="K14" s="8"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>signal_morse_received_text</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>signal_morse_received_text</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -643,10 +643,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
-        <x:v>signal_morse_received_notation</x:v>
+        <x:v>signal_morse_received_text</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>signal_morse_received_notation</x:v>
+        <x:v>signal_morse_received_text</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -668,10 +668,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>signal_morse_source</x:v>
+        <x:v>signal_morse_received_notation</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>signal_morse_source</x:v>
+        <x:v>signal_morse_received_notation</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -690,13 +690,13 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="8" t="str">
-        <x:v>integer</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
-        <x:v>signal_morse_dot_ms</x:v>
+        <x:v>signal_morse_source</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
-        <x:v>signal_morse_dot_ms</x:v>
+        <x:v>signal_morse_source</x:v>
       </x:c>
       <x:c r="D18" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -718,10 +718,10 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
-        <x:v>signal_morse_transitions</x:v>
+        <x:v>signal_morse_dot_ms</x:v>
       </x:c>
       <x:c r="C19" s="8" t="str">
-        <x:v>signal_morse_transitions</x:v>
+        <x:v>signal_morse_dot_ms</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -743,10 +743,10 @@
         <x:v>integer</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
-        <x:v>signal_morse_copies</x:v>
+        <x:v>signal_morse_transitions</x:v>
       </x:c>
       <x:c r="C20" s="8" t="str">
-        <x:v>signal_morse_copies</x:v>
+        <x:v>signal_morse_transitions</x:v>
       </x:c>
       <x:c r="D20" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -765,13 +765,13 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="8" t="str">
-        <x:v>decimal</x:v>
+        <x:v>integer</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
-        <x:v>signal_morse_consensus_confidence</x:v>
+        <x:v>signal_morse_copies</x:v>
       </x:c>
       <x:c r="C21" s="8" t="str">
-        <x:v>signal_morse_consensus_confidence</x:v>
+        <x:v>signal_morse_copies</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -790,13 +790,13 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>decimal</x:v>
       </x:c>
       <x:c r="B22" s="8" t="str">
-        <x:v>signal_morse_status</x:v>
+        <x:v>signal_morse_consensus_confidence</x:v>
       </x:c>
       <x:c r="C22" s="8" t="str">
-        <x:v>signal_morse_status</x:v>
+        <x:v>signal_morse_consensus_confidence</x:v>
       </x:c>
       <x:c r="D22" s="8" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -818,10 +818,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>signal_morse_error</x:v>
+        <x:v>signal_morse_status</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>signal_morse_error</x:v>
+        <x:v>signal_morse_status</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>Returned by MethodMesh.</x:v>
@@ -843,13 +843,13 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>methodmesh_full_json</x:v>
+        <x:v>signal_morse_error</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Full MethodMesh JSON</x:v>
+        <x:v>signal_morse_error</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>Complete execution result with provenance.</x:v>
+        <x:v>Returned by MethodMesh.</x:v>
       </x:c>
       <x:c r="E24"/>
       <x:c r="F24"/>
@@ -865,34 +865,38 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str">
-        <x:v>end group</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>run_signal_end</x:v>
-      </x:c>
-      <x:c r="C25"/>
-      <x:c r="D25"/>
+        <x:v>methodmesh_full_json</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Full MethodMesh JSON</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Complete execution result with provenance.</x:v>
+      </x:c>
       <x:c r="E25"/>
       <x:c r="F25"/>
       <x:c r="G25"/>
       <x:c r="H25"/>
-      <x:c r="I25"/>
+      <x:c r="I25" t="str">
+        <x:v>hidden-answer</x:v>
+      </x:c>
       <x:c r="J25"/>
-      <x:c r="K25"/>
+      <x:c r="K25" t="str">
+        <x:v>yes</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str">
-        <x:v>note</x:v>
+        <x:v>end group</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>return_summary</x:v>
-      </x:c>
-      <x:c r="C26" t="str">
-        <x:v>MethodMesh result captured.</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>Use methodmesh_full_json for the complete provenance record.</x:v>
-      </x:c>
+        <x:v>run_signal_end</x:v>
+      </x:c>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
       <x:c r="E26"/>
       <x:c r="F26"/>
       <x:c r="G26"/>
@@ -900,6 +904,27 @@
       <x:c r="I26"/>
       <x:c r="J26"/>
       <x:c r="K26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>note</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>return_summary</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>MethodMesh result captured.</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Use methodmesh_full_json for the complete provenance record.</x:v>
+      </x:c>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1278,6 +1303,39 @@
         <x:v>12 units</x:v>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>morse_source</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>manual</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Manual / human observed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>colour_assist</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>auto</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>Auto</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>colour_assist</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>off</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>Off</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1311,7 +1369,7 @@
         <x:v>signals_signal_morse_receive</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090906</x:v>
+        <x:v>2026091101</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
